--- a/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/pizzeria-50j-4m-5_60tr-constantd_def.xlsx
+++ b/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/pizzeria-50j-4m-5_60tr-constantd_def.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marinara #YL59</t>
+          <t>Pollo al pesto #XD13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mexicana #tL32</t>
+          <t>Mexicana #PL95</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bianca #Rt71</t>
+          <t>Vegetariana #BO26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Siciliana #jO06</t>
+          <t>Mexicana #aM44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -857,7 +857,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bianca #eu07</t>
+          <t>Marinara #Au09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mexicana #Ng07</t>
+          <t>Caprese #rG94</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -962,7 +962,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mediterránea #oz55</t>
+          <t>Hawaiana #nd26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hawaiana #EU76</t>
+          <t>Pepperoni #EY74</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Atún #xl82</t>
+          <t>Bianca #kX56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprese #VL27</t>
+          <t>Caprese #Rp08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1340,7 +1340,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Atún #iZ11</t>
+          <t>Mexicana #HI08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Margarita #ey26</t>
+          <t>Pollo al pesto #Bf24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Napolitana #tw15</t>
+          <t>Atún #bo81</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Atún #TW52</t>
+          <t>Atún #AZ23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Atún #wK99</t>
+          <t>Marinara #WA49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mexicana #yS99</t>
+          <t>Bianca #fS44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1844,7 +1844,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1865,7 +1865,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chicago style #QT50</t>
+          <t>Atún #PF97</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Carbonara #Zu66</t>
+          <t>Atún #rf16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Margarita #Py24</t>
+          <t>Vegetariana #mw17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2054,7 +2054,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pollo al pesto #mb03</t>
+          <t>Mediterránea #lq38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vegetariana #Lx40</t>
+          <t>Atún #RP00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2222,7 +2222,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2285,7 +2285,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cuatro quesos #eQ07</t>
+          <t>Picante #aJ97</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Atún #Ev65</t>
+          <t>Barbacoa #am35</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2432,7 +2432,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Chicago style #cI20</t>
+          <t>Hawaiana #QD26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2537,7 +2537,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mexicana #fl73</t>
+          <t>Mediterránea #tp37</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barbacoa #AU72</t>
+          <t>Hawaiana #SE00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2642,7 +2642,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bianca #WE60</t>
+          <t>Mediterránea #sR66</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2726,7 +2726,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2789,7 +2789,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Napolitana #LW03</t>
+          <t>Picante #jz73</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2810,7 +2810,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Prosciutto y rúcula #Vk37</t>
+          <t>Bianca #uA87</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2894,7 +2894,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2936,7 +2936,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Margarita #OH78</t>
+          <t>Caprese #we46</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bianca #ax23</t>
+          <t>Prosciutto y rúcula #oB98</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3125,7 +3125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Pollo al pesto #fs66</t>
+          <t>Prosciutto y rúcula #kX70</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Marinara #FN47</t>
+          <t>Margarita #nn39</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3272,7 +3272,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Marinara #Do73</t>
+          <t>Chicago style #fx50</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3314,7 +3314,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bianca #xc91</t>
+          <t>Mexicana #Vo25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3440,7 +3440,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3461,7 +3461,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hawaiana #oC65</t>
+          <t>Mediterránea #UF55</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pepperoni #zk16</t>
+          <t>Atún #FU69</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Cuatro quesos #nz20</t>
+          <t>Pollo al pesto #De49</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3650,7 +3650,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3692,7 +3692,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Pollo al pesto #vm20</t>
+          <t>Funghi (champiñones) #Gr26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3755,7 +3755,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3797,7 +3797,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Napolitana #Ye71</t>
+          <t>Cuatro quesos #nb99</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3818,7 +3818,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Mediterránea #sX89</t>
+          <t>Siciliana #og30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3923,7 +3923,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cuatro quesos #uG73</t>
+          <t>Atún #lc89</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4007,7 +4007,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4049,7 +4049,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pollo al pesto #JU24</t>
+          <t>Vegetariana #Im36</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4112,7 +4112,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hawaiana #wj93</t>
+          <t>Caprese #Nf14</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4154,7 +4154,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4175,7 +4175,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Atún #SS62</t>
+          <t>Mediterránea #tz71</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Margarita #hg21</t>
+          <t>Carbonara #IN01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4385,7 +4385,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Mexicana #xi72</t>
+          <t>Margarita #bK52</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Barbacoa #ej87</t>
+          <t>Carbonara #kB30</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4490,7 +4490,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4511,7 +4511,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4532,7 +4532,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Funghi (champiñones) #eA22</t>
+          <t>Hawaiana #SW97</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mexicana #dF82</t>
+          <t>Caprese #cN18</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
